--- a/CONSO_CUPRA.xlsx
+++ b/CONSO_CUPRA.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acocq\Desktop\PERSO\voitures\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\ProjetBorn\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D890AD27-027F-4F26-8EBF-AF530D61C153}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2C64048-210C-407F-86BB-586F2501D769}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F4A8DD21-A813-4214-B73F-010B05EB8AEB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F4A8DD21-A813-4214-B73F-010B05EB8AEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Feuil1!$A$1:$J$58</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Feuil1!$A$1:$J$54</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -221,18 +221,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.249977111117893"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -338,7 +332,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -349,7 +343,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
@@ -358,13 +352,13 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -373,19 +367,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -400,12 +385,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Milliers" xfId="1" builtinId="3"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -422,7 +404,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -738,22 +720,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAA5F25A-8661-4E6E-B62A-5B84C2FF51AB}">
-  <dimension ref="A1:J58"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:J54"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" style="1"/>
-    <col min="2" max="2" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="11.42578125" style="1"/>
-    <col min="8" max="8" width="17.28515625" style="5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.42578125" style="19" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="11.42578125" style="1"/>
+    <col min="1" max="1" width="11.44140625" style="1"/>
+    <col min="2" max="2" width="7.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="11.44140625" style="1"/>
+    <col min="8" max="8" width="17.33203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.44140625" style="16" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="11.44140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -772,7 +754,7 @@
       <c r="F1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="G1" s="12" t="s">
         <v>2</v>
       </c>
       <c r="H1" s="9" t="s">
@@ -781,11 +763,11 @@
       <c r="I1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="16" t="s">
+      <c r="J1" s="13" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>45925</v>
       </c>
@@ -804,20 +786,20 @@
       <c r="F2" s="8">
         <v>56</v>
       </c>
-      <c r="G2" s="20">
+      <c r="G2" s="17">
         <v>30</v>
       </c>
       <c r="H2" s="10">
-        <f>G2/F2</f>
+        <f t="shared" ref="H2:H33" si="0">G2/F2</f>
         <v>0.5357142857142857</v>
       </c>
       <c r="I2" s="10">
-        <f>F2/E2</f>
+        <f t="shared" ref="I2:I33" si="1">F2/E2</f>
         <v>1.3658536585365855</v>
       </c>
-      <c r="J2" s="18"/>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J2" s="15"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>45926</v>
       </c>
@@ -840,16 +822,16 @@
         <v>8</v>
       </c>
       <c r="H3" s="10">
-        <f>G3/F3</f>
+        <f t="shared" si="0"/>
         <v>0.72727272727272729</v>
       </c>
       <c r="I3" s="6">
-        <f>F3/E3</f>
+        <f t="shared" si="1"/>
         <v>1.375</v>
       </c>
       <c r="J3" s="2"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>45926</v>
       </c>
@@ -872,16 +854,16 @@
         <v>14</v>
       </c>
       <c r="H4" s="10">
-        <f>G4/F4</f>
+        <f t="shared" si="0"/>
         <v>0.28000000000000003</v>
       </c>
       <c r="I4" s="6">
-        <f>F4/E4</f>
+        <f t="shared" si="1"/>
         <v>1.25</v>
       </c>
       <c r="J4" s="2"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>45927</v>
       </c>
@@ -902,16 +884,16 @@
         <v>4.9400000000000004</v>
       </c>
       <c r="H5" s="10">
-        <f>G5/F5</f>
+        <f t="shared" si="0"/>
         <v>0.29058823529411765</v>
       </c>
       <c r="I5" s="6">
-        <f>F5/E5</f>
+        <f t="shared" si="1"/>
         <v>1.1333333333333333</v>
       </c>
       <c r="J5" s="2"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>45927</v>
       </c>
@@ -934,16 +916,16 @@
         <v>5.13</v>
       </c>
       <c r="H6" s="10">
-        <f>G6/F6</f>
+        <f t="shared" si="0"/>
         <v>0.56999999999999995</v>
       </c>
       <c r="I6" s="6">
-        <f>F6/E6</f>
+        <f t="shared" si="1"/>
         <v>0.81818181818181823</v>
       </c>
       <c r="J6" s="2"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>45927</v>
       </c>
@@ -966,18 +948,18 @@
         <v>29.78</v>
       </c>
       <c r="H7" s="10">
-        <f>G7/F7</f>
+        <f t="shared" si="0"/>
         <v>0.54145454545454552</v>
       </c>
       <c r="I7" s="6">
-        <f>F7/E7</f>
+        <f t="shared" si="1"/>
         <v>1.4864864864864864</v>
       </c>
-      <c r="J7" s="17">
+      <c r="J7" s="14">
         <v>1000</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>45945</v>
       </c>
@@ -1000,16 +982,16 @@
         <v>23.67</v>
       </c>
       <c r="H8" s="10">
-        <f>G8/F8</f>
+        <f t="shared" si="0"/>
         <v>0.51199411650191429</v>
       </c>
       <c r="I8" s="6">
-        <f>F8/E8</f>
+        <f t="shared" si="1"/>
         <v>0.82555357142857144</v>
       </c>
-      <c r="J8" s="17"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J8" s="14"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>45950</v>
       </c>
@@ -1032,16 +1014,16 @@
         <v>2.16</v>
       </c>
       <c r="H9" s="10">
-        <f>G9/F9</f>
+        <f t="shared" si="0"/>
         <v>0.39495337356006582</v>
       </c>
       <c r="I9" s="6">
-        <f>F9/E9</f>
+        <f t="shared" si="1"/>
         <v>0.18230000000000002</v>
       </c>
-      <c r="J9" s="17"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J9" s="14"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>45957</v>
       </c>
@@ -1064,16 +1046,16 @@
         <v>25.73</v>
       </c>
       <c r="H10" s="10">
-        <f>G10/F10</f>
+        <f t="shared" si="0"/>
         <v>0.50719495367632572</v>
       </c>
       <c r="I10" s="6">
-        <f>F10/E10</f>
+        <f t="shared" si="1"/>
         <v>0.84549999999999992</v>
       </c>
-      <c r="J10" s="17"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J10" s="14"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>45965</v>
       </c>
@@ -1096,16 +1078,16 @@
         <v>24.64</v>
       </c>
       <c r="H11" s="10">
-        <f>G11/F11</f>
+        <f t="shared" si="0"/>
         <v>0.51181920152881055</v>
       </c>
       <c r="I11" s="6">
-        <f>F11/E11</f>
+        <f t="shared" si="1"/>
         <v>0.80236666666666667</v>
       </c>
-      <c r="J11" s="17"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J11" s="14"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>45969</v>
       </c>
@@ -1126,16 +1108,16 @@
         <v>14.2</v>
       </c>
       <c r="H12" s="10">
-        <f>G12/F12</f>
+        <f t="shared" si="0"/>
         <v>0.53417597712823983</v>
       </c>
       <c r="I12" s="6">
-        <f>F12/E12</f>
+        <f t="shared" si="1"/>
         <v>1.0224230769230769</v>
       </c>
-      <c r="J12" s="17"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J12" s="14"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <v>45974</v>
       </c>
@@ -1156,16 +1138,16 @@
         <v>14.28</v>
       </c>
       <c r="H13" s="10">
-        <f>G13/F13</f>
+        <f t="shared" si="0"/>
         <v>0.53797468354430378</v>
       </c>
       <c r="I13" s="6">
-        <f>F13/E13</f>
+        <f t="shared" si="1"/>
         <v>1.5614117647058823</v>
       </c>
-      <c r="J13" s="17"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J13" s="14"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>45983</v>
       </c>
@@ -1186,16 +1168,16 @@
         <v>24.82</v>
       </c>
       <c r="H14" s="10">
-        <f>G14/F14</f>
+        <f t="shared" si="0"/>
         <v>0.68797294675277887</v>
       </c>
       <c r="I14" s="6">
-        <f>F14/E14</f>
+        <f t="shared" si="1"/>
         <v>1.4430799999999999</v>
       </c>
-      <c r="J14" s="17"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J14" s="14"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>45985</v>
       </c>
@@ -1218,16 +1200,16 @@
         <v>4.66</v>
       </c>
       <c r="H15" s="10">
-        <f>G15/F15</f>
+        <f t="shared" si="0"/>
         <v>0.27637743906055395</v>
       </c>
       <c r="I15" s="6">
-        <f>F15/E15</f>
+        <f t="shared" si="1"/>
         <v>0.1852857142857143</v>
       </c>
-      <c r="J15" s="17"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J15" s="14"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>45989</v>
       </c>
@@ -1250,16 +1232,16 @@
         <v>10.94</v>
       </c>
       <c r="H16" s="10">
-        <f>G16/F16</f>
+        <f t="shared" si="0"/>
         <v>0.39578886436814875</v>
       </c>
       <c r="I16" s="6">
-        <f>F16/E16</f>
+        <f t="shared" si="1"/>
         <v>0.18551006711409396</v>
       </c>
-      <c r="J16" s="17"/>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J16" s="14"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <v>45990</v>
       </c>
@@ -1282,16 +1264,16 @@
         <v>14.52</v>
       </c>
       <c r="H17" s="10">
-        <f>G17/F17</f>
+        <f t="shared" si="0"/>
         <v>0.59277403551745245</v>
       </c>
       <c r="I17" s="6">
-        <f>F17/E17</f>
+        <f t="shared" si="1"/>
         <v>1.3608333333333333</v>
       </c>
       <c r="J17" s="2"/>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
         <v>45990</v>
       </c>
@@ -1312,16 +1294,16 @@
         <v>17.04</v>
       </c>
       <c r="H18" s="10">
-        <f>G18/F18</f>
+        <f t="shared" si="0"/>
         <v>0.70106146630461608</v>
       </c>
       <c r="I18" s="6">
-        <f>F18/E18</f>
+        <f t="shared" si="1"/>
         <v>1.6204000000000001</v>
       </c>
       <c r="J18" s="2"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
         <v>45991</v>
       </c>
@@ -1342,16 +1324,16 @@
         <v>21.56</v>
       </c>
       <c r="H19" s="10">
-        <f>G19/F19</f>
+        <f t="shared" si="0"/>
         <v>0.3918788738026428</v>
       </c>
       <c r="I19" s="6">
-        <f>F19/E19</f>
+        <f t="shared" si="1"/>
         <v>1.6181470588235296</v>
       </c>
-      <c r="J19" s="17"/>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J19" s="14"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
         <v>45991</v>
       </c>
@@ -1374,16 +1356,16 @@
         <v>30.19</v>
       </c>
       <c r="H20" s="10">
-        <f>G20/F20</f>
+        <f t="shared" si="0"/>
         <v>0.68439426913311574</v>
       </c>
       <c r="I20" s="6">
-        <f>F20/E20</f>
+        <f t="shared" si="1"/>
         <v>0.72314754098360656</v>
       </c>
       <c r="J20" s="2"/>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
         <v>45991</v>
       </c>
@@ -1406,16 +1388,16 @@
         <v>10.71</v>
       </c>
       <c r="H21" s="10">
-        <f>G21/F21</f>
+        <f t="shared" si="0"/>
         <v>0.27783542596243643</v>
       </c>
       <c r="I21" s="6">
-        <f>F21/E21</f>
+        <f t="shared" si="1"/>
         <v>1.133764705882353</v>
       </c>
       <c r="J21" s="2"/>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
         <v>45996</v>
       </c>
@@ -1437,16 +1419,16 @@
         <v>18.78</v>
       </c>
       <c r="H22" s="10">
-        <f>G22/F22</f>
+        <f t="shared" si="0"/>
         <v>0.6739637538130272</v>
       </c>
       <c r="I22" s="6">
-        <f>F22/E22</f>
+        <f t="shared" si="1"/>
         <v>0.79614285714285715</v>
       </c>
-      <c r="J22" s="17"/>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J22" s="14"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
         <v>45998</v>
       </c>
@@ -1468,16 +1450,16 @@
         <v>15.4</v>
       </c>
       <c r="H23" s="10">
-        <f>G23/F23</f>
+        <f t="shared" si="0"/>
         <v>0.38535645472061658</v>
       </c>
       <c r="I23" s="6">
-        <f>F23/E23</f>
+        <f t="shared" si="1"/>
         <v>1.5985199999999999</v>
       </c>
-      <c r="J23" s="17"/>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J23" s="14"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
         <v>46008</v>
       </c>
@@ -1499,16 +1481,16 @@
         <v>20.76</v>
       </c>
       <c r="H24" s="10">
-        <f>G24/F24</f>
+        <f t="shared" si="0"/>
         <v>0.5383398594507689</v>
       </c>
       <c r="I24" s="6">
-        <f>F24/E24</f>
+        <f t="shared" si="1"/>
         <v>1.5425200000000001</v>
       </c>
-      <c r="J24" s="17"/>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J24" s="14"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
         <v>46011</v>
       </c>
@@ -1530,16 +1512,16 @@
         <v>10.02</v>
       </c>
       <c r="H25" s="10">
-        <f>G25/F25</f>
+        <f t="shared" si="0"/>
         <v>0.40897959183673466</v>
       </c>
       <c r="I25" s="6">
-        <f>F25/E25</f>
+        <f t="shared" si="1"/>
         <v>0.40833333333333333</v>
       </c>
-      <c r="J25" s="17"/>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J25" s="14"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="3">
         <v>46014</v>
       </c>
@@ -1561,16 +1543,16 @@
         <v>31.54</v>
       </c>
       <c r="H26" s="10">
-        <f>G26/F26</f>
+        <f t="shared" si="0"/>
         <v>0.67750735720576549</v>
       </c>
       <c r="I26" s="6">
-        <f>F26/E26</f>
+        <f t="shared" si="1"/>
         <v>1.5517666666666665</v>
       </c>
-      <c r="J26" s="17"/>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J26" s="14"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="3">
         <v>46021</v>
       </c>
@@ -1592,16 +1574,16 @@
         <v>31</v>
       </c>
       <c r="H27" s="10">
-        <f>G27/F27</f>
+        <f t="shared" si="0"/>
         <v>0.53866203301476978</v>
       </c>
       <c r="I27" s="6">
-        <f>F27/E27</f>
+        <f t="shared" si="1"/>
         <v>1.6442857142857141</v>
       </c>
-      <c r="J27" s="17"/>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J27" s="14"/>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="3">
         <v>46021</v>
       </c>
@@ -1623,16 +1605,16 @@
         <v>6.97</v>
       </c>
       <c r="H28" s="10">
-        <f>G28/F28</f>
+        <f t="shared" si="0"/>
         <v>0.53847342398022247</v>
       </c>
       <c r="I28" s="6">
-        <f>F28/E28</f>
+        <f t="shared" si="1"/>
         <v>1.0786666666666667</v>
       </c>
-      <c r="J28" s="18"/>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J28" s="15"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="3">
         <v>46031</v>
       </c>
@@ -1653,16 +1635,16 @@
         <v>33.58</v>
       </c>
       <c r="H29" s="10">
-        <f>G29/F29</f>
+        <f t="shared" si="0"/>
         <v>0.53863304621208474</v>
       </c>
       <c r="I29" s="6">
-        <f>F29/E29</f>
+        <f t="shared" si="1"/>
         <v>1.2723061224489796</v>
       </c>
-      <c r="J29" s="17"/>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J29" s="14"/>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="3">
         <v>46032</v>
       </c>
@@ -1683,16 +1665,16 @@
         <v>5.74</v>
       </c>
       <c r="H30" s="10">
-        <f>G30/F30</f>
+        <f t="shared" si="0"/>
         <v>0.53841103086014452</v>
       </c>
       <c r="I30" s="6">
-        <f>F30/E30</f>
+        <f t="shared" si="1"/>
         <v>0.71073333333333333</v>
       </c>
-      <c r="J30" s="17"/>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J30" s="14"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="3">
         <v>46039</v>
       </c>
@@ -1713,16 +1695,16 @@
         <v>30.83</v>
       </c>
       <c r="H31" s="10">
-        <f>G31/F31</f>
+        <f t="shared" si="0"/>
         <v>0.65595744680851065</v>
       </c>
       <c r="I31" s="6">
-        <f>F31/E31</f>
+        <f t="shared" si="1"/>
         <v>1.88</v>
       </c>
-      <c r="J31" s="17"/>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J31" s="14"/>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="3">
         <v>46051</v>
       </c>
@@ -1745,16 +1727,16 @@
         <v>3.99</v>
       </c>
       <c r="H32" s="10">
-        <f>G32/F32</f>
+        <f t="shared" si="0"/>
         <v>0.53860691144708428</v>
       </c>
       <c r="I32" s="6">
-        <f>F32/E32</f>
+        <f t="shared" si="1"/>
         <v>0.67345454545454553</v>
       </c>
-      <c r="J32" s="17"/>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J32" s="14"/>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" s="3">
         <v>46052</v>
       </c>
@@ -1777,16 +1759,16 @@
         <v>29.95</v>
       </c>
       <c r="H33" s="10">
-        <f>G33/F33</f>
+        <f t="shared" si="0"/>
         <v>0.51207960743413061</v>
       </c>
       <c r="I33" s="6">
-        <f>F33/E33</f>
+        <f t="shared" si="1"/>
         <v>0.83552857142857151</v>
       </c>
-      <c r="J33" s="17"/>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J33" s="14"/>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" s="3">
         <v>46062</v>
       </c>
@@ -1809,18 +1791,18 @@
         <v>28.17</v>
       </c>
       <c r="H34" s="10">
-        <f>G34/F34</f>
+        <f t="shared" ref="H34:H54" si="2">G34/F34</f>
         <v>0.51218181818181818</v>
       </c>
       <c r="I34" s="6">
-        <f>F34/E34</f>
+        <f t="shared" ref="I34:I54" si="3">F34/E34</f>
         <v>0.83333333333333337</v>
       </c>
-      <c r="J34" s="17">
+      <c r="J34" s="14">
         <v>6156</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" s="3">
         <v>46067</v>
       </c>
@@ -1841,16 +1823,16 @@
         <v>19.350000000000001</v>
       </c>
       <c r="H35" s="10">
-        <f>G35/F35</f>
+        <f t="shared" si="2"/>
         <v>0.58999298716346016</v>
       </c>
       <c r="I35" s="6">
-        <f>F35/E35</f>
+        <f t="shared" si="3"/>
         <v>1.8220555555555553</v>
       </c>
-      <c r="J35" s="17"/>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J35" s="14"/>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" s="3">
         <v>46068</v>
       </c>
@@ -1871,16 +1853,16 @@
         <v>0.64</v>
       </c>
       <c r="H36" s="10">
-        <f>G36/F36</f>
+        <f t="shared" si="2"/>
         <v>0.41025641025641024</v>
       </c>
       <c r="I36" s="6">
-        <f>F36/E36</f>
+        <f t="shared" si="3"/>
         <v>0.19500000000000001</v>
       </c>
-      <c r="J36" s="17"/>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J36" s="14"/>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" s="3">
         <v>46068</v>
       </c>
@@ -1901,16 +1883,16 @@
         <v>14.25</v>
       </c>
       <c r="H37" s="10">
-        <f>G37/F37</f>
+        <f t="shared" si="2"/>
         <v>0.39543789543789543</v>
       </c>
       <c r="I37" s="6">
-        <f>F37/E37</f>
+        <f t="shared" si="3"/>
         <v>1.8018000000000001</v>
       </c>
-      <c r="J37" s="17"/>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J37" s="14"/>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" s="3">
         <v>46071</v>
       </c>
@@ -1931,16 +1913,16 @@
         <v>29.96</v>
       </c>
       <c r="H38" s="10">
-        <f>G38/F38</f>
+        <f t="shared" si="2"/>
         <v>0.51218052825027782</v>
       </c>
       <c r="I38" s="6">
-        <f>F38/E38</f>
+        <f t="shared" si="3"/>
         <v>0.83564285714285713</v>
       </c>
-      <c r="J38" s="17"/>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J38" s="14"/>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" s="3">
         <v>46073</v>
       </c>
@@ -1961,16 +1943,16 @@
         <v>6.97</v>
       </c>
       <c r="H39" s="10">
-        <f>G39/F39</f>
+        <f t="shared" si="2"/>
         <v>0.5385982536125492</v>
       </c>
       <c r="I39" s="6">
-        <f>F39/E39</f>
+        <f t="shared" si="3"/>
         <v>0.76123529411764712</v>
       </c>
-      <c r="J39" s="17"/>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J39" s="14"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" s="3">
         <v>46076</v>
       </c>
@@ -1991,16 +1973,16 @@
         <v>12.81</v>
       </c>
       <c r="H40" s="10">
-        <f>G40/F40</f>
+        <f t="shared" si="2"/>
         <v>0.53837101790367325</v>
       </c>
       <c r="I40" s="6">
-        <f>F40/E40</f>
+        <f t="shared" si="3"/>
         <v>1.1330476190476191</v>
       </c>
-      <c r="J40" s="17"/>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J40" s="14"/>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" s="3">
         <v>46081</v>
       </c>
@@ -2021,16 +2003,16 @@
         <v>20.13</v>
       </c>
       <c r="H41" s="10">
-        <f>G41/F41</f>
+        <f t="shared" si="2"/>
         <v>0.67892074198988195</v>
       </c>
       <c r="I41" s="6">
-        <f>F41/E41</f>
+        <f t="shared" si="3"/>
         <v>1.5605263157894735</v>
       </c>
-      <c r="J41" s="17"/>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J41" s="14"/>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" s="3">
         <v>46081</v>
       </c>
@@ -2051,16 +2033,16 @@
         <v>10.24</v>
       </c>
       <c r="H42" s="10">
-        <f>G42/F42</f>
+        <f t="shared" si="2"/>
         <v>0.53894736842105262</v>
       </c>
       <c r="I42" s="6">
-        <f>F42/E42</f>
+        <f t="shared" si="3"/>
         <v>0.82608695652173914</v>
       </c>
-      <c r="J42" s="17"/>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J42" s="14"/>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" s="3">
         <v>46088</v>
       </c>
@@ -2081,16 +2063,16 @@
         <v>33.04</v>
       </c>
       <c r="H43" s="10">
-        <f>G43/F43</f>
+        <f t="shared" si="2"/>
         <v>0.59242258521453794</v>
       </c>
       <c r="I43" s="6">
-        <f>F43/E43</f>
+        <f t="shared" si="3"/>
         <v>1.8590333333333333</v>
       </c>
-      <c r="J43" s="17"/>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J43" s="14"/>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" s="3">
         <v>46098</v>
       </c>
@@ -2111,16 +2093,16 @@
         <v>27.01</v>
       </c>
       <c r="H44" s="10">
-        <f>G44/F44</f>
+        <f t="shared" si="2"/>
         <v>0.46854129442989234</v>
       </c>
       <c r="I44" s="6">
-        <f>F44/E44</f>
+        <f t="shared" si="3"/>
         <v>0.83546376811594203</v>
       </c>
-      <c r="J44" s="17"/>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J44" s="14"/>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" s="3">
         <v>46101</v>
       </c>
@@ -2141,16 +2123,16 @@
         <v>18.79</v>
       </c>
       <c r="H45" s="10">
-        <f>G45/F45</f>
+        <f t="shared" si="2"/>
         <v>0.69402378665878695</v>
       </c>
       <c r="I45" s="6">
-        <f>F45/E45</f>
+        <f t="shared" si="3"/>
         <v>1.1280833333333333</v>
       </c>
-      <c r="J45" s="17"/>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J45" s="14"/>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" s="3">
         <v>46108</v>
       </c>
@@ -2171,16 +2153,16 @@
         <v>23.23</v>
       </c>
       <c r="H46" s="10">
-        <f>G46/F46</f>
+        <f t="shared" si="2"/>
         <v>0.53852930267062316</v>
       </c>
       <c r="I46" s="6">
-        <f>F46/E46</f>
+        <f t="shared" si="3"/>
         <v>1.0520975609756098</v>
       </c>
-      <c r="J46" s="17"/>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J46" s="14"/>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" s="3">
         <v>46109</v>
       </c>
@@ -2201,16 +2183,16 @@
         <v>2.27</v>
       </c>
       <c r="H47" s="10">
-        <f>G47/F47</f>
+        <f t="shared" si="2"/>
         <v>0.75140681893412775</v>
       </c>
       <c r="I47" s="6">
-        <f>F47/E47</f>
+        <f t="shared" si="3"/>
         <v>0.37762499999999999</v>
       </c>
-      <c r="J47" s="17"/>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J47" s="14"/>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" s="3">
         <v>46109</v>
       </c>
@@ -2231,16 +2213,16 @@
         <v>27.96</v>
       </c>
       <c r="H48" s="10">
-        <f>G48/F48</f>
+        <f t="shared" si="2"/>
         <v>0.69715254575375252</v>
       </c>
       <c r="I48" s="6">
-        <f>F48/E48</f>
+        <f t="shared" si="3"/>
         <v>2.1108421052631581</v>
       </c>
-      <c r="J48" s="17"/>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J48" s="14"/>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" s="3">
         <v>46111</v>
       </c>
@@ -2261,16 +2243,16 @@
         <v>50.05</v>
       </c>
       <c r="H49" s="10">
-        <f>G49/F49</f>
+        <f t="shared" si="2"/>
         <v>0.71636108606352056</v>
       </c>
       <c r="I49" s="6">
-        <f>F49/E49</f>
+        <f t="shared" si="3"/>
         <v>1.7466750000000002</v>
       </c>
-      <c r="J49" s="17"/>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J49" s="14"/>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" s="3">
         <v>46111</v>
       </c>
@@ -2291,16 +2273,16 @@
         <v>29.05</v>
       </c>
       <c r="H50" s="10">
-        <f>G50/F50</f>
+        <f t="shared" si="2"/>
         <v>0.72528899208548681</v>
       </c>
       <c r="I50" s="6">
-        <f>F50/E50</f>
+        <f t="shared" si="3"/>
         <v>1.2137272727272725</v>
       </c>
-      <c r="J50" s="17"/>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J50" s="14"/>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" s="3">
         <v>46111</v>
       </c>
@@ -2321,16 +2303,16 @@
         <v>19.52</v>
       </c>
       <c r="H51" s="10">
-        <f>G51/F51</f>
+        <f t="shared" si="2"/>
         <v>0.659994590208277</v>
       </c>
       <c r="I51" s="6">
-        <f>F51/E51</f>
+        <f t="shared" si="3"/>
         <v>1.0562857142857143</v>
       </c>
-      <c r="J51" s="17"/>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J51" s="14"/>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" s="3">
         <v>46111</v>
       </c>
@@ -2351,16 +2333,16 @@
         <v>34.81</v>
       </c>
       <c r="H52" s="10">
-        <f>G52/F52</f>
+        <f t="shared" si="2"/>
         <v>0.59301533219761504</v>
       </c>
       <c r="I52" s="6">
-        <f>F52/E52</f>
+        <f t="shared" si="3"/>
         <v>1.5864864864864865</v>
       </c>
-      <c r="J52" s="17"/>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J52" s="14"/>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" s="3">
         <v>46112</v>
       </c>
@@ -2381,16 +2363,16 @@
         <v>44.89</v>
       </c>
       <c r="H53" s="10">
-        <f>G53/F53</f>
+        <f t="shared" si="2"/>
         <v>0.65565390120643829</v>
       </c>
       <c r="I53" s="6">
-        <f>F53/E53</f>
+        <f t="shared" si="3"/>
         <v>1.7116499999999999</v>
       </c>
-      <c r="J53" s="17"/>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J53" s="14"/>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" s="3">
         <v>46114</v>
       </c>
@@ -2411,86 +2393,23 @@
         <v>10.029999999999999</v>
       </c>
       <c r="H54" s="10">
-        <f>G54/F54</f>
+        <f t="shared" si="2"/>
         <v>0.53855240549828176</v>
       </c>
       <c r="I54" s="6">
-        <f>F54/E54</f>
+        <f t="shared" si="3"/>
         <v>1.1639999999999999</v>
       </c>
-      <c r="J54" s="17"/>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A55" s="3"/>
-      <c r="B55" s="2"/>
-      <c r="C55" s="2"/>
-      <c r="D55" s="2"/>
-      <c r="E55" s="2"/>
-      <c r="F55" s="8"/>
-      <c r="G55" s="11"/>
-      <c r="H55" s="10"/>
-      <c r="I55" s="6"/>
-      <c r="J55" s="17"/>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A56" s="3"/>
-      <c r="B56" s="2"/>
-      <c r="C56" s="2"/>
-      <c r="D56" s="2"/>
-      <c r="E56" s="2"/>
-      <c r="F56" s="8"/>
-      <c r="G56" s="11"/>
-      <c r="H56" s="10"/>
-      <c r="I56" s="6"/>
-      <c r="J56" s="17"/>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A57" s="3"/>
-      <c r="B57" s="2"/>
-      <c r="C57" s="2"/>
-      <c r="D57" s="2"/>
-      <c r="E57" s="2"/>
-      <c r="F57" s="8"/>
-      <c r="G57" s="11"/>
-      <c r="H57" s="10"/>
-      <c r="I57" s="6"/>
-      <c r="J57" s="17"/>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A58" s="2"/>
-      <c r="B58" s="2"/>
-      <c r="C58" s="2"/>
-      <c r="D58" s="2"/>
-      <c r="E58" s="12" t="e">
-        <f>AVERAGE(E59:E60)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F58" s="14" t="e">
-        <f>AVERAGE(F59:F60)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G58" s="21">
-        <f>SUM(G59:G80)</f>
-        <v>0</v>
-      </c>
-      <c r="H58" s="13" t="e">
-        <f>AVERAGE(H59:H91)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I58" s="12" t="e">
-        <f>AVERAGE(I59:I60)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J58" s="12"/>
+      <c r="J54" s="14"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J58" xr:uid="{AAA5F25A-8661-4E6E-B62A-5B84C2FF51AB}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J58">
-      <sortCondition ref="A1:A58"/>
+  <autoFilter ref="A1:J54" xr:uid="{AAA5F25A-8661-4E6E-B62A-5B84C2FF51AB}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J54">
+      <sortCondition ref="A1:A54"/>
     </sortState>
   </autoFilter>
-  <conditionalFormatting sqref="H3:H58">
-    <cfRule type="colorScale" priority="11">
+  <conditionalFormatting sqref="H3:H54">
+    <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2500,7 +2419,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="12">
+    <cfRule type="colorScale" priority="15">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2511,8 +2430,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I58">
-    <cfRule type="colorScale" priority="13">
+  <conditionalFormatting sqref="I3:I54">
+    <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
